--- a/PRODUCCION EVENTOS.xlsx
+++ b/PRODUCCION EVENTOS.xlsx
@@ -5276,7 +5276,7 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">

--- a/PRODUCCION EVENTOS.xlsx
+++ b/PRODUCCION EVENTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hearstspain-my.sharepoint.com/personal/japaricio_hearst_es/Documents/_MARKETING/_ESTRATEGIA/_FACTURACIÓN EN LA WEB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="13_ncr:1_{08A27A2F-4016-4143-89CF-C963FB5C8DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{658B8739-6208-44D2-85BB-5F87EB4EBA33}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{08A27A2F-4016-4143-89CF-C963FB5C8DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B69B6F5F-F714-4398-8D50-D55FEADEEFBB}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14278" uniqueCount="1732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14279" uniqueCount="1733">
   <si>
     <t>Mes inserción</t>
   </si>
@@ -5232,6 +5232,9 @@
   </si>
   <si>
     <t>2026/000006603</t>
+  </si>
+  <si>
+    <t>INSERCIONES</t>
   </si>
 </sst>
 </file>
@@ -5279,7 +5282,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5308,6 +5311,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -5341,7 +5350,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5356,6 +5365,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5699,14 +5711,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S885"/>
+  <dimension ref="A1:T885"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="9.77734375" style="1" customWidth="1"/>
     <col min="20" max="16384" width="12.21875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5764,8 +5776,11 @@
       <c r="S1" s="2" t="s">
         <v>1729</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T1" s="6" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -5824,7 +5839,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -5880,7 +5895,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
@@ -5936,7 +5951,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
@@ -5992,7 +6007,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
@@ -6048,7 +6063,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
@@ -6107,7 +6122,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>38</v>
       </c>
@@ -6163,7 +6178,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
@@ -6219,7 +6234,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>38</v>
       </c>
@@ -6275,7 +6290,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -6331,7 +6346,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
@@ -6387,7 +6402,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -6446,7 +6461,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -6502,7 +6517,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
@@ -6561,7 +6576,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
